--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/MstExchangeQuotationInfo001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/MstExchangeQuotationInfo001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2712" windowWidth="14652" windowHeight="3600"/>
+    <workbookView xWindow="0" yWindow="2715" windowWidth="14655" windowHeight="3600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,11 +12,12 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>货币对</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -26,31 +27,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>数据来源</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开盘价</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收盘价</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最低价</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最高价</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中间价</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>报价单位</t>
+    <t>开盘价（元）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收盘价（元）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中间价（元）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最高价（元）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最低价（元）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -397,16 +390,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" customWidth="1"/>
-    <col min="7" max="8" width="12.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="12.75" customWidth="1"/>
+    <col min="6" max="7" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -423,25 +416,14 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C30">
-      <formula1>"行内,calypso,中债登,外汇交易中心,中证登,专家法,央行,外管局,上清所"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -450,7 +432,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -460,7 +442,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
